--- a/System3_Master_MRI_Control.xlsx
+++ b/System3_Master_MRI_Control.xlsx
@@ -525,7 +525,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>680944481ba71834fe59dfab5e937fd43afa6609</t>
+          <t>e44fb454bde3431da479bb4ecf48b094e49ae69d</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -551,7 +551,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2/7 pass</t>
+          <t>None/None pass</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>680944481ba71834fe59dfab5e937fd43afa6609</t>
+          <t>146eb69b697f86559d50519f8eaee3c8fbb8a82c</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>main=680944481ba71834fe59dfab5e937fd43afa6609 serving=680944481ba71834fe59dfab5e937fd43afa6609</t>
+          <t>main=e44fb454bde3431da479bb4ecf48b094e49ae69d serving=e44fb454bde3431da479bb4ecf48b094e49ae69d</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>API deploy/info 2026-08-19T23:09:57Z</t>
+          <t>API deploy/info 2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -2173,7 +2173,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -2203,7 +2203,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>open_prs=20</t>
+          <t>open_prs=64</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>gh pr list 2026-08-19T23:09:57Z</t>
+          <t>gh pr list 2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>github main 680944481ba71834fe59dfab5e937fd43afa6609 + code path</t>
+          <t>github main e44fb454bde3431da479bb4ecf48b094e49ae69d + code path</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>github main 680944481ba71834fe59dfab5e937fd43afa6609 + code path</t>
+          <t>github main e44fb454bde3431da479bb4ecf48b094e49ae69d + code path</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>github main 680944481ba71834fe59dfab5e937fd43afa6609 + code path</t>
+          <t>github main e44fb454bde3431da479bb4ecf48b094e49ae69d + code path</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>connected=True auth=AUTH_OK v=279</t>
+          <t>connected=True auth=AUTH_OK v=321</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>/api/broker/status 2026-08-19T23:09:57Z</t>
+          <t>/api/broker/status 2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>connected=True auth=AUTH_OK v=279</t>
+          <t>connected=True auth=AUTH_OK v=321</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>/api/broker/status 2026-08-19T23:09:57Z</t>
+          <t>/api/broker/status 2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>/api/auto_gates 2026-08-19T23:09:57Z</t>
+          <t>/api/auto_gates 2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -3527,12 +3527,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>['ohlc:HTTP_429:{"data":{"805":"Too many requests. Further requests may result in the user being blocked."},"status":"failed"}']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>NOT_PROVEN</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -3616,24 +3616,32 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>api_contracts=488 smoke_contracts=488</t>
+          <t>api_contracts=462 smoke_contracts=None</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>/api/batch/chains + smoke394 2026-08-19T15:44:27.830949+00:00</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+          <t>/api/batch/chains + smoke394 None</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>warm race / semantic source incomplete</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>warm race / semantic source incomplete</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3663,7 +3671,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -3697,24 +3705,32 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>api_contracts=488 smoke_contracts=488</t>
+          <t>api_contracts=462 smoke_contracts=None</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>/api/batch/chains + smoke394 2026-08-19T15:44:27.830949+00:00</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+          <t>/api/batch/chains + smoke394 None</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>warm race / semantic source incomplete</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>warm race / semantic source incomplete</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3744,7 +3760,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -3778,24 +3794,32 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>api_contracts=488 smoke_contracts=488</t>
+          <t>api_contracts=462 smoke_contracts=None</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>/api/batch/chains + smoke394 2026-08-19T15:44:27.830949+00:00</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+          <t>/api/batch/chains + smoke394 None</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>warm race / semantic source incomplete</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>warm race / semantic source incomplete</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3825,7 +3849,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -3859,24 +3883,32 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>api_contracts=488 smoke_contracts=488</t>
+          <t>api_contracts=462 smoke_contracts=None</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>/api/batch/chains + smoke394 2026-08-19T15:44:27.830949+00:00</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+          <t>/api/batch/chains + smoke394 None</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>warm race / semantic source incomplete</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>warm race / semantic source incomplete</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3906,7 +3938,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -3946,7 +3978,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3991,7 +4023,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4053,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>tabs_with_wait=11</t>
+          <t>tabs_with_wait=0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -4076,7 +4108,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4138,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>gate_pass=False blocker=SYS3-BLK-003</t>
+          <t>gate_pass=False blocker=None</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -4116,7 +4148,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>/api/auto_gates 2026-08-19T23:09:57Z</t>
+          <t>/api/auto_gates 2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -4161,7 +4193,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -4201,7 +4233,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -4246,7 +4278,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -4286,7 +4318,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -4331,7 +4363,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -4371,7 +4403,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -4416,7 +4448,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -4456,7 +4488,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4501,7 +4533,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4573,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4586,7 +4618,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4658,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4671,7 +4703,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4743,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4756,7 +4788,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -4796,7 +4828,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -4841,7 +4873,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -4885,7 +4917,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>/api/auto_gates 2026-08-19T23:09:57Z</t>
+          <t>/api/auto_gates 2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -4922,7 +4954,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4994,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -5007,7 +5039,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -5047,7 +5079,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -5092,7 +5124,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5164,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -5177,7 +5209,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -5217,7 +5249,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -5262,7 +5294,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -5296,7 +5328,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>gate_pass=False blocker=SYS3-BLK-005</t>
+          <t>gate_pass=False blocker=None</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5306,19 +5338,11 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>/api/auto_gates 2026-08-19T23:09:57Z</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>SYS3-BLK-005</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>SYS3-BLK-005</t>
-        </is>
-      </c>
+          <t>/api/auto_gates 2026-08-27T08:17:13Z</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -5351,7 +5375,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5415,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -5436,7 +5460,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -5476,19 +5500,11 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>/api/auto_gates 2026-08-19T23:09:57Z</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>SYS3-BLK-008</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>SYS3-BLK-008</t>
-        </is>
-      </c>
+          <t>/api/auto_gates 2026-08-27T08:17:13Z</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -5521,7 +5537,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -5561,7 +5577,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -5606,7 +5622,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -5640,24 +5656,24 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>qc_status=PASS</t>
+          <t>qc_status=NOT_READY</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>/api/health 2026-08-19T23:09:57Z</t>
+          <t>/api/health 2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5687,7 +5703,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -5772,7 +5788,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -5816,7 +5832,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>/api/agent/status 2026-08-19T23:09:57Z</t>
+          <t>/api/agent/status 2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -5861,7 +5877,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -5891,7 +5907,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>resume_serving_sha=738d9dd2d324478e553b61c6881b26dbd380195f live=680944481ba71834fe59dfab5e937fd43afa6609</t>
+          <t>resume_serving_sha=None live=e44fb454bde3431da479bb4ecf48b094e49ae69d</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5946,7 +5962,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -6027,7 +6043,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
     </row>
@@ -6612,7 +6628,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6627,7 +6643,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>680944481ba71834fe59dfab5e937fd43afa6609</t>
+          <t>e44fb454bde3431da479bb4ecf48b094e49ae69d</t>
         </is>
       </c>
     </row>
@@ -6659,7 +6675,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6706,7 +6722,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6800,7 +6816,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6815,7 +6831,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2/7</t>
+          <t>None/None</t>
         </is>
       </c>
     </row>
@@ -6847,7 +6863,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6862,7 +6878,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>680944481ba71834fe59dfab5e937fd43afa6609</t>
+          <t>146eb69b697f86559d50519f8eaee3c8fbb8a82c</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7242,12 +7258,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>#291</t>
+          <t>#377</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>feat/repo-clean-forensic-toolkit-v1-2-actions-storage-20260819</t>
+          <t>feat/data-lake-ingestion-376</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -7257,7 +7273,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>feat(cleanup): exact-digest GitHub Actions storage evidence</t>
+          <t>feat(data-lake): scaffold GCS ingestion/storage module</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -7277,19 +7293,19 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-18T22:11:58Z</t>
+          <t>2026-08-27T07:52:43Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>#286</t>
+          <t>#353</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>fix/20260819-scheduler-health-verifier-diagnostics</t>
+          <t>docs/ruhi-user-reference-20260824</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -7299,7 +7315,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>test(control-plane): add fail-closed scheduler-health diagnostic gate</t>
+          <t>docs(ruhi): publish user recommendation reference pack</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -7319,19 +7335,19 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-19T04:28:05Z</t>
+          <t>2026-08-26T19:26:10Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>#279</t>
+          <t>#348</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>docs/chatgpt-current-handoff-20260818</t>
+          <t>feat/github-control-monitor-20260824</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -7341,7 +7357,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>docs(chatgpt): current live handoff + Cursor instruction slot</t>
+          <t>feat(control-plane): add GitHub closure monitor ledger</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -7361,19 +7377,19 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-08-18T05:01:01Z</t>
+          <t>2026-08-24T15:21:54Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>#262</t>
+          <t>#336</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>dependabot/github_actions/actions/checkout-7</t>
+          <t>docs/perplexity-independent-forensic-controller-20260824</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -7383,7 +7399,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>chore(deps): bump actions/checkout from 4 to 7</t>
+          <t>docs(coordination): add Perplexity independent forensic controller handoff</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -7403,19 +7419,19 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-17T06:37:33Z</t>
+          <t>2026-08-25T14:02:02Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>#261</t>
+          <t>#335</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>dependabot/github_actions/actions/upload-artifact-7</t>
+          <t>chatgpt/same-document-ui-semantic-proof-20260824</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -7425,7 +7441,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>chore(deps): bump actions/upload-artifact from 6 to 7</t>
+          <t>test(ui): preserve one hydrated document across semantic tab proof</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -7445,19 +7461,19 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-08-17T06:37:27Z</t>
+          <t>2026-08-24T12:03:23Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>#260</t>
+          <t>#324</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>dependabot/npm_and_yarn/dashboard/frontend/radix-ui/react-dropdown-menu-2.1.24</t>
+          <t>docs/catalyst-early-warning-plan-20260822</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7467,7 +7483,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>chore(deps): bump @radix-ui/react-dropdown-menu from 2.1.18 to 2.1.24 in /dashboard/frontend</t>
+          <t>docs(catalyst): add Catalyst Early Warning Intelligence implementation authority</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -7487,19 +7503,19 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-08-16T21:04:09Z</t>
+          <t>2026-08-22T11:42:27Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>#242</t>
+          <t>#323</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>audit/cursor-full-cloud-ui-forensic-20260816T062501Z</t>
+          <t>cursor/ui-closure-rule-2b45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -7509,7 +7525,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>docs(audit): full cloud+UI forensic package 20260816T062501Z</t>
+          <t>docs(ruhi): lock Cursor permanent UI-closure rule</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -7529,19 +7545,19 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-08-16T08:06:09Z</t>
+          <t>2026-08-22T11:01:51Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>#240</t>
+          <t>#317</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fix/live-chain-source-layout-proof-20260816</t>
+          <t>docs/cursor-coordination-contract-20260822</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -7551,7 +7567,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>fix(proof): align chain-source parser with production UI layout</t>
+          <t>docs(cursor): enforce multi-agent coordination and proof contract</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -7561,7 +7577,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -7571,19 +7587,19 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-08-16T17:59:50Z</t>
+          <t>2026-08-22T13:34:51Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>#219</t>
+          <t>#315</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>fix/20260815-full-ui-truth-gate</t>
+          <t>docs/central-agent-coordination-20260822</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -7593,7 +7609,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>fix(ui): enforce all 22 tabs and option-chain semantic truth</t>
+          <t>docs: add permanent central multi-agent coordination ledger</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -7603,7 +7619,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -7613,19 +7629,19 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-08-15T06:45:10Z</t>
+          <t>2026-08-22T00:54:38Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>#217</t>
+          <t>#314</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>fix/dependabot-vite-safe-major</t>
+          <t>cursor/cloud-agent-env-setup-9d91</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -7635,7 +7651,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>security: keep Vite Dependabot updates on compatible remediation major</t>
+          <t>chore(env): Cloud Agent dev environment setup for the System3 dashboard</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -7655,19 +7671,19 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-08-14T17:36:59Z</t>
+          <t>2026-08-22T00:05:51Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>#215</t>
+          <t>#304</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>dependabot/pip/statsmodels-gte-0.14.6</t>
+          <t>docs/codex-ruhi-execution</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -7677,7 +7693,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>build(deps): update statsmodels requirement from &gt;=0.14.2 to &gt;=0.14.6</t>
+          <t>docs: add Codex CLI RUHI execution guide</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -7697,19 +7713,19 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-08-14T17:20:41Z</t>
+          <t>2026-08-21T08:48:27Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>#214</t>
+          <t>#291</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>dependabot/pip/pyotp-2.10.0</t>
+          <t>feat/repo-clean-forensic-toolkit-v1-2-actions-storage-20260819</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -7719,7 +7735,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>build(deps): bump pyotp from 2.9.0 to 2.10.0</t>
+          <t>feat(cleanup): exact-digest GitHub Actions storage evidence</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -7739,19 +7755,19 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-08-14T17:20:37Z</t>
+          <t>2026-08-18T22:11:58Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>#213</t>
+          <t>#286</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>dependabot/pip/yamllint-1.38.0</t>
+          <t>fix/20260819-scheduler-health-verifier-diagnostics</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -7761,7 +7777,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>build(deps): bump yamllint from 1.35.1 to 1.38.0</t>
+          <t>test(control-plane): add fail-closed scheduler-health diagnostic gate</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -7781,19 +7797,19 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-08-14T17:20:33Z</t>
+          <t>2026-08-19T04:28:05Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>#212</t>
+          <t>#279</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>dependabot/pip/jugaad-data-gte-0.35.2</t>
+          <t>docs/chatgpt-current-handoff-20260818</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -7803,7 +7819,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>build(deps): update jugaad-data requirement from &gt;=0.31.1 to &gt;=0.35.2</t>
+          <t>docs(chatgpt): current live handoff + Cursor instruction slot</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7823,19 +7839,19 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-08-14T17:15:44Z</t>
+          <t>2026-08-18T05:01:01Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>#211</t>
+          <t>#261</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>dependabot/pip/yfinance-gte-1.5.2</t>
+          <t>dependabot/github_actions/actions/upload-artifact-7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -7845,7 +7861,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>build(deps): update yfinance requirement from &gt;=0.2.38 to &gt;=1.5.2</t>
+          <t>chore(deps): bump actions/upload-artifact from 4 to 7</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7865,19 +7881,19 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-08-14T17:14:54Z</t>
+          <t>2026-08-26T18:49:23Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>#209</t>
+          <t>#242</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>dependabot/github_actions/SonarSource/sonarqube-scan-action-8</t>
+          <t>audit/cursor-full-cloud-ui-forensic-20260816T062501Z</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -7887,7 +7903,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>build(deps): bump SonarSource/sonarqube-scan-action from 7 to 8</t>
+          <t>docs(audit): full cloud+UI forensic package 20260816T062501Z</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7907,19 +7923,19 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-08-14T16:49:24Z</t>
+          <t>2026-08-16T08:06:09Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>#208</t>
+          <t>#217</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>dependabot/github_actions/actions/setup-python-7</t>
+          <t>fix/dependabot-vite-safe-major</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -7929,7 +7945,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>chore(deps): bump actions/setup-python from 5 to 7</t>
+          <t>security: keep Vite Dependabot updates on compatible remediation major</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7949,19 +7965,19 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-17T06:37:33Z</t>
+          <t>2026-08-14T17:36:59Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>#207</t>
+          <t>#215</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>dependabot/pip/dashboard/backend/numpy-2.5.2</t>
+          <t>dependabot/pip/statsmodels-gte-0.14.6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -7971,7 +7987,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>build(deps): bump numpy from 2.2.6 to 2.5.2 in /dashboard/backend</t>
+          <t>build(deps): update statsmodels requirement from &gt;=0.14.2 to &gt;=0.14.6</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -7991,19 +8007,19 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-08-14T16:49:12Z</t>
+          <t>2026-08-14T17:20:41Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>#206</t>
+          <t>#214</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>dependabot/pip/dashboard/backend/uvicorn-0.52.1</t>
+          <t>dependabot/pip/pyotp-2.10.0</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -8013,7 +8029,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>build(deps): bump uvicorn from 0.49.0 to 0.52.1 in /dashboard/backend</t>
+          <t>build(deps): bump pyotp from 2.9.0 to 2.10.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8033,49 +8049,1897 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-08-14T16:49:06Z</t>
+          <t>2026-08-14T17:20:37Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>#213</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>dependabot/pip/yamllint-1.38.0</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>build(deps): bump yamllint from 1.35.1 to 1.38.0</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-08-14T17:20:33Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>#212</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>dependabot/pip/jugaad-data-gte-0.35.2</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>build(deps): update jugaad-data requirement from &gt;=0.31.1 to &gt;=0.35.2</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-08-14T17:15:44Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>#211</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>dependabot/pip/yfinance-gte-1.5.2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>build(deps): update yfinance requirement from &gt;=0.2.38 to &gt;=1.5.2</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-08-14T17:14:54Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>#209</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>dependabot/github_actions/SonarSource/sonarqube-scan-action-8</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>chore(deps): bump SonarSource/sonarqube-scan-action from 7 to 8</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-08-26T18:49:34Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>#208</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>dependabot/github_actions/actions/setup-python-7</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>chore(deps): bump actions/setup-python from 5 to 7</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-08-26T18:50:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>#207</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>dependabot/pip/dashboard/backend/numpy-2.5.2</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>build(deps): bump numpy from 2.2.6 to 2.5.2 in /dashboard/backend</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-08-14T16:49:12Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>#206</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>dependabot/pip/dashboard/backend/uvicorn-0.52.1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>build(deps): bump uvicorn from 0.49.0 to 0.52.1 in /dashboard/backend</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2026-08-14T16:49:06Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>#205</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>dependabot/pip/dashboard/backend/google-cloud-secret-manager-gte-2.30.0-and-lt-3.0.0</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>UNASSIGNED</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>build(deps): update google-cloud-secret-manager requirement from &lt;3.0.0,&gt;=2.20.0 to &gt;=2.30.0,&lt;3.0.0 in /dashboard/backend</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>NOT_PROVEN</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>PR author</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>2026-08-14T16:49:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>#203</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>dependabot/npm_and_yarn/dashboard/frontend/recharts-3.10.1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>build(deps): bump recharts from 2.15.4 to 3.10.1 in /dashboard/frontend</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026-08-14T16:48:32Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>#202</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>dependabot/npm_and_yarn/dashboard/frontend/tailwind-merge-3.6.0</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>build(deps): bump tailwind-merge from 2.6.1 to 3.6.0 in /dashboard/frontend</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026-08-14T16:48:24Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>#201</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>dependabot/npm_and_yarn/dashboard/frontend/lucide-react-1.31.0</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>build(deps): bump lucide-react from 0.294.0 to 1.31.0 in /dashboard/frontend</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026-08-14T16:48:19Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>#200</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>dependabot/npm_and_yarn/dashboard/frontend/typescript-7.0.2</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>chore(deps-dev): bump typescript from 5.9.3 to 7.0.2 in /dashboard/frontend</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2026-08-16T15:36:55Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>#199</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>dependabot/pip/dashboard/backend/pandas-3.0.5</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>build(deps): bump pandas from 2.3.3 to 3.0.5 in /dashboard/backend</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2026-08-14T16:48:09Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>#197</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>dependabot/pip/dashboard/backend/fastapi-0.141.1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>build(deps): bump fastapi from 0.138.0 to 0.141.1 in /dashboard/backend</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2026-08-14T16:48:04Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>#196</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>dependabot/github_actions/actions/setup-node-7</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>chore(deps): bump actions/setup-node from 4 to 7</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2026-08-26T18:49:29Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>#195</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>dependabot/docker/python-3.14-slim</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>build(deps): bump python from 3.10-slim to 3.14-slim</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2026-08-14T16:48:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>#192</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>fix/20260814-paper-url-truth-gate</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>fix(paper): durable Cloud Run paper ledger + semantic URL truth gates</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2026-08-14T08:53:43Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>#191</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>fix/ui-option-parity-proof-20260814</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>test(gcp): make production option-chain UI parity a post-deploy gate</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2026-08-14T04:43:23Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>#189</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>feat/market-data-readonly-failover-20260814</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>feat(data): read-only broker market-data failover core</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2026-08-14T04:01:45Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>#182</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>fix/frontend-typecheck-gate-20260814</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>test(frontend): strict TypeScript gate — repair pass 2</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2026-08-13T21:24:51Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>#165</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>fix/ui-semantic-hydration-typecheck-20260813</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Harden production UI semantic hydration proof</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2026-08-13T14:38:07Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>#139</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>feat/ui-mobile-shell-review</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>feat(ui): reclaim mobile workspace with compact navigation</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:52:28Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>#131</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>fix/public-readonly-runtime-slice</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>security: current-main public-readonly runtime boundary</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2026-08-12T07:34:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>#129</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>fix/permanent-public-dashboard-no-key</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>security: permanently remove dashboard credential and session authority</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2026-08-12T04:53:59Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>#125</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>feat/sre-operations-truth-v1</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>feat(sre): add fail-closed OperationsTruth inventory and SLO scorecard</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2026-08-12T00:44:49Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>#121</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>feat/gcp-observability-phase1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>feat(observability): add traced read-only 24x7 monitoring foundation</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2026-08-11T23:40:13Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>#115</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>fix/no-key-deploy-proof-contract-20260812</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>fix(gcp): make Cloud Run static proof command-aware</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2026-08-11T21:57:31Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>#110</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>fix/gcp-atomic-runtime-spec-20260811</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>fix(gcp): deploy one canonical Cloud Run runtime revision</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2026-08-11T16:25:16Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>#98</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>fix/dashboard-vcloak-css-issue-44</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>fix(dashboard): add missing [v-cloak] CSS rule to hide raw template t…</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2026-08-11T11:18:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>#97</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>fix/paper-pnl-synthetic-data-guard-20260811</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>fix(dashboard): guard live P&amp;L sync against synthetic/paper-simulatio…</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2026-08-10T23:55:29Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>#84</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>copilot/fix-negative-holdout-issues</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Harden analyzer-only frozen evaluation and ML proof gating for unreliable holdout/UI states</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2026-08-10T17:12:29Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>#83</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>copilot/implement-p0-stabilization-patch</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>[WIP] Implement P0 stabilization patch for trading reliability and GCP migration</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:01:24Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>#81</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>feat/nonlive-equity-options-bigdata-pipeline</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>feat(research): resumable all-equity options big-data and leakage-safe backtest</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:30:13Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>#80</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>fix-paper-console-truth-mobile</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>fix(ui): paper console status and mobile layout</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2026-07-07T06:14:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>#78</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>fix/core-pipeline-v8-paper-ledger</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>feat(paper): add core pipeline v8 paper ledger and proof</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2026-07-06T18:49:42Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>#76</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>copilot/verify-remediate-github-actions</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Normalize cloud runtime check output for dashboard-auth-protected endpoints</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2026-07-06T10:44:48Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>#67</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>copilot/fix-blocking-workflow-policy-issue</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Fix blocking workflow-policy guard by restoring single-workflow layout</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2026-07-03T18:23:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>#65</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>fix-render-api-502-readonly-stability</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Stabilize dashboard API polling</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2026-07-05T08:21:18Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>#51</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>chatgpt/cloud-forensic-gates-20260701</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>docs: add cloud CI failure triage proof</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2026-07-01T08:54:24Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>#43</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>cloud-live-ui-paper-prediction-proof</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Add corrected cloud dashboard proof workflow</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2026-06-24T07:18:04Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>#42</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>copilot/complete-dashboard-enhancement</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>[WIP] Implement all recommended features for dashboard enhancement</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>2026-06-24T13:51:02Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>#41</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>copilot/complete-trader-audit-phase-1</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>[WIP] Add comprehensive audit endpoints for trading system</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2026-06-23T17:17:38Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>#40</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>copilot/phase-1-backend-api-expansion</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>[WIP] Expand backend API for portfolio overview and details</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2026-06-23T17:12:30Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>#39</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>copilot/full-production-readiness-audit</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>[WIP] Conduct dashboard production readiness audit</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2026-06-23T17:06:49Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>#38</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>copilot/activate-dhan-data-api</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>UNASSIGNED</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>[WIP] Activate Dhan Data API as P0 source with token safety measures</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>NOT_PROVEN</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>PR author</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>2026-06-23T17:02:46Z</t>
         </is>
       </c>
     </row>
@@ -8153,7 +10017,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>680944481ba71834fe59dfab5e937fd43afa6609</t>
+          <t>e44fb454bde3431da479bb4ecf48b094e49ae69d</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -8163,7 +10027,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>680944481ba71834fe59dfab5e937fd43afa6609</t>
+          <t>e44fb454bde3431da479bb4ecf48b094e49ae69d</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -8191,7 +10055,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>680944481ba71834fe59dfab5e937fd43afa6609</t>
+          <t>e44fb454bde3431da479bb4ecf48b094e49ae69d</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -8201,7 +10065,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>680944481ba71834fe59dfab5e937fd43afa6609</t>
+          <t>e44fb454bde3431da479bb4ecf48b094e49ae69d</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -8233,7 +10097,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>680944481ba71834fe59dfab5e937fd43afa6609</t>
+          <t>e44fb454bde3431da479bb4ecf48b094e49ae69d</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -8243,7 +10107,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>680944481ba71834fe59dfab5e937fd43afa6609</t>
+          <t>e44fb454bde3431da479bb4ecf48b094e49ae69d</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -8278,7 +10142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8336,299 +10200,6 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Next Action</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>main_sha_parity</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>680944481ba71834fe59dfab5e937fd43afa6609</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>680944481ba71834fe59dfab5e937fd43afa6609</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>680944481ba71834fe59dfab5e937fd43afa6609</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>680944481ba71834fe59dfab5e937fd43afa6609</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-08-19T23:09:57Z</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Re-run scan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>local_vs_main</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>680944481ba71834fe59dfab5e937fd43afa6609</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>680944481ba71834fe59dfab5e937fd43afa6609</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>680944481ba71834fe59dfab5e937fd43afa6609</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-08-19T23:09:57Z</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Re-run scan</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>chain_api_NIFTY</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>488</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>NOT_PROVEN_WITHOUT_FRESH_BROWSER</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>POPULATED</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-08-19T23:09:57Z</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Re-run scan</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chain_api_BANKNIFTY</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>762</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>NOT_PROVEN_WITHOUT_FRESH_BROWSER</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>POPULATED</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2026-08-19T23:09:57Z</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Re-run scan</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>chain_api_FINNIFTY</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>510</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>NOT_PROVEN_WITHOUT_FRESH_BROWSER</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>POPULATED</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2026-08-19T23:09:57Z</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Re-run scan</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>chain_api_MIDCPNIFTY</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>550</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>NOT_PROVEN_WITHOUT_FRESH_BROWSER</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>POPULATED</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2026-08-19T23:09:57Z</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Re-run scan</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>continuous_closure_resume</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>738d9dd2d324478e553b61c6881b26dbd380195f</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>680944481ba71834fe59dfab5e937fd43afa6609</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>680944481ba71834fe59dfab5e937fd43afa6609</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>680944481ba71834fe59dfab5e937fd43afa6609</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>STALE_ARTIFACT</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2026-08-19T23:09:57Z</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Re-run scan</t>
         </is>
       </c>
     </row>
@@ -8728,7 +10299,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>contracts=488 status=MARKET_CLOSED_DHAN_SNAPSHOT</t>
+          <t>contracts=462 status=None</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -8738,7 +10309,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8780,7 +10351,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>contracts=762 status=MARKET_CLOSED_DHAN_SNAPSHOT</t>
+          <t>contracts=714 status=None</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -8790,7 +10361,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8832,7 +10403,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>contracts=510 status=MARKET_CLOSED_DHAN_SNAPSHOT</t>
+          <t>contracts=478 status=None</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -8842,7 +10413,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -8884,7 +10455,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>contracts=550 status=MARKET_CLOSED_DHAN_SNAPSHOT</t>
+          <t>contracts=506 status=None</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -8894,7 +10465,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-19T23:09:57Z</t>
+          <t>2026-08-27T08:17:13Z</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
